--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2019_coquimbo_provincial.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2019_coquimbo_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 00:29</t>
+    <t xml:space="preserve">2026-10-05 05:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
